--- a/results/gmac_snr6dB/gmac_snr6dB_classB_Ru34_Rv34_SC/classB_Ru34_Rv34_snr6dB_SC.xlsx
+++ b/results/gmac_snr6dB/gmac_snr6dB_classB_Ru34_Rv34_SC/classB_Ru34_Rv34_snr6dB_SC.xlsx
@@ -473,7 +473,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Gaussian MAC — Class B, (Ru=0.34, Rv=0.34), SNR=6dB, SC (L=1), pure_MC design</t>
+          <t>Gaussian MAC — Class B, (Ru=0.34, Rv=0.34), SNR=6dB, SC (L=1)</t>
         </is>
       </c>
     </row>

--- a/results/gmac_snr6dB/gmac_snr6dB_classB_Ru34_Rv34_SC/classB_Ru34_Rv34_snr6dB_SC.xlsx
+++ b/results/gmac_snr6dB/gmac_snr6dB_classB_Ru34_Rv34_SC/classB_Ru34_Rv34_snr6dB_SC.xlsx
@@ -650,10 +650,10 @@
         <v>0.6875</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0002</v>
+        <v>0.000385</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>5000</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="10">
@@ -679,7 +679,7 @@
         <v>0</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>5000</v>
+        <v>13000</v>
       </c>
     </row>
     <row r="11">
@@ -702,10 +702,10 @@
         <v>0.6875</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0</v>
+        <v>0.0002</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>5000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="12">
@@ -734,6 +734,7 @@
         <v>3000</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>

--- a/results/gmac_snr6dB/gmac_snr6dB_classB_Ru34_Rv34_SC/classB_Ru34_Rv34_snr6dB_SC.xlsx
+++ b/results/gmac_snr6dB/gmac_snr6dB_classB_Ru34_Rv34_SC/classB_Ru34_Rv34_snr6dB_SC.xlsx
@@ -728,13 +728,12 @@
         <v>0.6875</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="13"/>
+        <v>10000</v>
+      </c>
+    </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
